--- a/MR_gwas/gMR_res.xlsx
+++ b/MR_gwas/gMR_res.xlsx
@@ -127,19 +127,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8169972721519051</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.6449674875535427</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.9890270567502675</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.08777029826447058</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.2982495603869879E-20</v>
+        <v>0.8150727019066166</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.6414547207912324</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9886906830220008</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.08858060260988987</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.530508621360337E-20</v>
       </c>
     </row>
   </sheetData>

--- a/MR_gwas/gMR_res.xlsx
+++ b/MR_gwas/gMR_res.xlsx
@@ -550,28 +550,28 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.23011913258685218</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.14925497334793525</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.3109832918257691</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.04125722410148824</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2.4376317070633728E-8</v>
+        <v>0.23236872185860305</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.15211455637328183</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3126228873439243</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.04094600279863327</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.3868556953420557E-8</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2587499591362141</v>
+        <v>1.2615848169774782</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1609689676187018</v>
+        <v>1.1642936060457407</v>
       </c>
       <c r="J2" t="n">
-        <v>1.3647664182405637</v>
+        <v>1.3670059185788994</v>
       </c>
     </row>
   </sheetData>

--- a/MR_gwas/gMR_res.xlsx
+++ b/MR_gwas/gMR_res.xlsx
@@ -127,19 +127,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8150727019066166</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.6414547207912324</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.9886906830220008</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.08858060260988987</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3.530508621360337E-20</v>
+        <v>0.8169972721519051</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.6449674875535427</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9890270567502675</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.08777029826447058</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.2982495603869879E-20</v>
       </c>
     </row>
   </sheetData>

--- a/MR_gwas/gMR_res.xlsx
+++ b/MR_gwas/gMR_res.xlsx
@@ -127,19 +127,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8169972721519051</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.6449674875535427</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.9890270567502675</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.08777029826447058</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.2982495603869879E-20</v>
+        <v>0.8150727019066166</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.6414547207912324</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9886906830220008</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.08858060260988987</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.530508621360337E-20</v>
       </c>
     </row>
   </sheetData>
@@ -550,28 +550,28 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.23236872185860305</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.15211455637328183</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.3126228873439243</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.04094600279863327</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.3868556953420557E-8</v>
+        <v>0.41316696180467066</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3254540976326379</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.5008798259767034</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.04475146131226161</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.6443764249560108E-20</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2615848169774782</v>
+        <v>1.5115973838934877</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1642936060457407</v>
+        <v>1.3846592737389758</v>
       </c>
       <c r="J2" t="n">
-        <v>1.3670059185788994</v>
+        <v>1.6501724968220384</v>
       </c>
     </row>
   </sheetData>
